--- a/output/lady_lake/TestEnvData_Database.xlsx
+++ b/output/lady_lake/TestEnvData_Database.xlsx
@@ -482,7 +482,7 @@
         <v>06/02/2025</v>
       </c>
       <c r="B2" t="str">
-        <v>$4,440.29</v>
+        <v>$176.74</v>
       </c>
       <c r="C2" t="str">
         <v>206 Book Transfer Credit</v>
@@ -516,7 +516,7 @@
         <v>06/02/2025</v>
       </c>
       <c r="B4" t="str">
-        <v>$11,587.01</v>
+        <v>$4,440.29</v>
       </c>
       <c r="C4" t="str">
         <v>206 Book Transfer Credit</v>
@@ -533,7 +533,7 @@
         <v>06/02/2025</v>
       </c>
       <c r="B5" t="str">
-        <v>$176.74</v>
+        <v>$11,587.01</v>
       </c>
       <c r="C5" t="str">
         <v>206 Book Transfer Credit</v>
@@ -550,7 +550,7 @@
         <v>06/03/2025</v>
       </c>
       <c r="B6" t="str">
-        <v>$17,031.44</v>
+        <v>$6,113.09</v>
       </c>
       <c r="C6" t="str">
         <v>206 Book Transfer Credit</v>
@@ -567,7 +567,7 @@
         <v>06/03/2025</v>
       </c>
       <c r="B7" t="str">
-        <v>$6,113.09</v>
+        <v>$17,031.44</v>
       </c>
       <c r="C7" t="str">
         <v>206 Book Transfer Credit</v>
@@ -601,7 +601,7 @@
         <v>06/04/2025</v>
       </c>
       <c r="B9" t="str">
-        <v>$10,225.28</v>
+        <v>$5,909.75</v>
       </c>
       <c r="C9" t="str">
         <v>206 Book Transfer Credit</v>
@@ -618,7 +618,7 @@
         <v>06/04/2025</v>
       </c>
       <c r="B10" t="str">
-        <v>$5,909.75</v>
+        <v>$10,225.28</v>
       </c>
       <c r="C10" t="str">
         <v>206 Book Transfer Credit</v>
@@ -635,7 +635,7 @@
         <v>06/05/2025</v>
       </c>
       <c r="B11" t="str">
-        <v>$26,014.50</v>
+        <v>$5,084.96</v>
       </c>
       <c r="C11" t="str">
         <v>206 Book Transfer Credit</v>
@@ -652,7 +652,7 @@
         <v>06/05/2025</v>
       </c>
       <c r="B12" t="str">
-        <v>$57,793.75</v>
+        <v>$26,014.50</v>
       </c>
       <c r="C12" t="str">
         <v>206 Book Transfer Credit</v>
@@ -669,7 +669,7 @@
         <v>06/05/2025</v>
       </c>
       <c r="B13" t="str">
-        <v>$5,084.96</v>
+        <v>$57,793.75</v>
       </c>
       <c r="C13" t="str">
         <v>206 Book Transfer Credit</v>
@@ -686,13 +686,13 @@
         <v>06/06/2025</v>
       </c>
       <c r="B14" t="str">
-        <v>$284,288.95</v>
+        <v>$379.64</v>
       </c>
       <c r="C14" t="str">
-        <v>201 Individual Automatic Transfer Credit</v>
+        <v>206 Book Transfer Credit</v>
       </c>
       <c r="D14" t="str">
-        <v>SWEEP TRANSFER FROM</v>
+        <v>FROM DEBIT ACCOUNT BANK:</v>
       </c>
       <c r="E14" t="str">
         <v>-</v>
@@ -720,7 +720,7 @@
         <v>06/06/2025</v>
       </c>
       <c r="B16" t="str">
-        <v>$379.64</v>
+        <v>$15,244.21</v>
       </c>
       <c r="C16" t="str">
         <v>206 Book Transfer Credit</v>
@@ -737,13 +737,13 @@
         <v>06/06/2025</v>
       </c>
       <c r="B17" t="str">
-        <v>$15,244.21</v>
+        <v>$284,288.95</v>
       </c>
       <c r="C17" t="str">
-        <v>206 Book Transfer Credit</v>
+        <v>201 Individual Automatic Transfer Credit</v>
       </c>
       <c r="D17" t="str">
-        <v>FROM DEBIT ACCOUNT BANK:</v>
+        <v>SWEEP TRANSFER FROM</v>
       </c>
       <c r="E17" t="str">
         <v>-</v>
@@ -754,7 +754,7 @@
         <v>06/09/2025</v>
       </c>
       <c r="B18" t="str">
-        <v>$199,787.28</v>
+        <v>$167,823.80</v>
       </c>
       <c r="C18" t="str">
         <v>206 Book Transfer Credit</v>
@@ -771,7 +771,7 @@
         <v>06/09/2025</v>
       </c>
       <c r="B19" t="str">
-        <v>$167,823.80</v>
+        <v>$199,787.28</v>
       </c>
       <c r="C19" t="str">
         <v>206 Book Transfer Credit</v>
@@ -788,7 +788,7 @@
         <v>06/10/2025</v>
       </c>
       <c r="B20" t="str">
-        <v>$18,232.78</v>
+        <v>$3,461.00</v>
       </c>
       <c r="C20" t="str">
         <v>206 Book Transfer Credit</v>
@@ -805,7 +805,7 @@
         <v>06/10/2025</v>
       </c>
       <c r="B21" t="str">
-        <v>$3,461.00</v>
+        <v>$18,232.78</v>
       </c>
       <c r="C21" t="str">
         <v>206 Book Transfer Credit</v>
@@ -822,7 +822,7 @@
         <v>06/11/2025</v>
       </c>
       <c r="B22" t="str">
-        <v>$3,806.55</v>
+        <v>$2,649.95</v>
       </c>
       <c r="C22" t="str">
         <v>206 Book Transfer Credit</v>
@@ -839,7 +839,7 @@
         <v>06/11/2025</v>
       </c>
       <c r="B23" t="str">
-        <v>$140,008.81</v>
+        <v>$3,806.55</v>
       </c>
       <c r="C23" t="str">
         <v>206 Book Transfer Credit</v>
@@ -856,7 +856,7 @@
         <v>06/11/2025</v>
       </c>
       <c r="B24" t="str">
-        <v>$2,649.95</v>
+        <v>$140,008.81</v>
       </c>
       <c r="C24" t="str">
         <v>206 Book Transfer Credit</v>
@@ -873,7 +873,7 @@
         <v>06/12/2025</v>
       </c>
       <c r="B25" t="str">
-        <v>$28,439.88</v>
+        <v>$3,830.29</v>
       </c>
       <c r="C25" t="str">
         <v>206 Book Transfer Credit</v>
@@ -890,7 +890,7 @@
         <v>06/12/2025</v>
       </c>
       <c r="B26" t="str">
-        <v>$3,830.29</v>
+        <v>$28,439.88</v>
       </c>
       <c r="C26" t="str">
         <v>206 Book Transfer Credit</v>
@@ -992,7 +992,7 @@
         <v>06/17/2025</v>
       </c>
       <c r="B32" t="str">
-        <v>$3,290.00</v>
+        <v>$466.99</v>
       </c>
       <c r="C32" t="str">
         <v>206 Book Transfer Credit</v>
@@ -1009,7 +1009,7 @@
         <v>06/17/2025</v>
       </c>
       <c r="B33" t="str">
-        <v>$466.99</v>
+        <v>$3,290.00</v>
       </c>
       <c r="C33" t="str">
         <v>206 Book Transfer Credit</v>
@@ -1026,7 +1026,7 @@
         <v>06/18/2025</v>
       </c>
       <c r="B34" t="str">
-        <v>$13,807.40</v>
+        <v>$1,874.72</v>
       </c>
       <c r="C34" t="str">
         <v>206 Book Transfer Credit</v>
@@ -1043,7 +1043,7 @@
         <v>06/18/2025</v>
       </c>
       <c r="B35" t="str">
-        <v>$1,874.72</v>
+        <v>$13,807.40</v>
       </c>
       <c r="C35" t="str">
         <v>206 Book Transfer Credit</v>
@@ -1060,13 +1060,13 @@
         <v>06/20/2025</v>
       </c>
       <c r="B36" t="str">
-        <v>$292,988.16</v>
+        <v>$1,904.00</v>
       </c>
       <c r="C36" t="str">
-        <v>201 Individual Automatic Transfer Credit</v>
+        <v>206 Book Transfer Credit</v>
       </c>
       <c r="D36" t="str">
-        <v>SWEEP TRANSFER FROM</v>
+        <v>FROM DEBIT ACCOUNT BANK:</v>
       </c>
       <c r="E36" t="str">
         <v>-</v>
@@ -1077,7 +1077,7 @@
         <v>06/20/2025</v>
       </c>
       <c r="B37" t="str">
-        <v>$1,904.00</v>
+        <v>$14,195.21</v>
       </c>
       <c r="C37" t="str">
         <v>206 Book Transfer Credit</v>
@@ -1111,13 +1111,13 @@
         <v>06/20/2025</v>
       </c>
       <c r="B39" t="str">
-        <v>$14,195.21</v>
+        <v>$292,988.16</v>
       </c>
       <c r="C39" t="str">
-        <v>206 Book Transfer Credit</v>
+        <v>201 Individual Automatic Transfer Credit</v>
       </c>
       <c r="D39" t="str">
-        <v>FROM DEBIT ACCOUNT BANK:</v>
+        <v>SWEEP TRANSFER FROM</v>
       </c>
       <c r="E39" t="str">
         <v>-</v>
@@ -1230,7 +1230,7 @@
         <v>06/25/2025</v>
       </c>
       <c r="B46" t="str">
-        <v>$291,638.14</v>
+        <v>$66,054.98</v>
       </c>
       <c r="C46" t="str">
         <v>206 Book Transfer Credit</v>
@@ -1247,7 +1247,7 @@
         <v>06/25/2025</v>
       </c>
       <c r="B47" t="str">
-        <v>$66,054.98</v>
+        <v>$291,638.14</v>
       </c>
       <c r="C47" t="str">
         <v>206 Book Transfer Credit</v>
@@ -1264,7 +1264,7 @@
         <v>06/26/2025</v>
       </c>
       <c r="B48" t="str">
-        <v>$9,008.50</v>
+        <v>$120.00</v>
       </c>
       <c r="C48" t="str">
         <v>206 Book Transfer Credit</v>
@@ -1298,7 +1298,7 @@
         <v>06/26/2025</v>
       </c>
       <c r="B50" t="str">
-        <v>$120.00</v>
+        <v>$9,008.50</v>
       </c>
       <c r="C50" t="str">
         <v>206 Book Transfer Credit</v>
@@ -1315,7 +1315,7 @@
         <v>06/27/2025</v>
       </c>
       <c r="B51" t="str">
-        <v>$9,667.14</v>
+        <v>$770.00</v>
       </c>
       <c r="C51" t="str">
         <v>206 Book Transfer Credit</v>
@@ -1332,7 +1332,7 @@
         <v>06/27/2025</v>
       </c>
       <c r="B52" t="str">
-        <v>$51,794.28</v>
+        <v>$9,667.14</v>
       </c>
       <c r="C52" t="str">
         <v>206 Book Transfer Credit</v>
@@ -1349,7 +1349,7 @@
         <v>06/27/2025</v>
       </c>
       <c r="B53" t="str">
-        <v>$770.00</v>
+        <v>$51,794.28</v>
       </c>
       <c r="C53" t="str">
         <v>206 Book Transfer Credit</v>
@@ -1366,7 +1366,7 @@
         <v>06/30/2025</v>
       </c>
       <c r="B54" t="str">
-        <v>$29,479.49</v>
+        <v>$976.36</v>
       </c>
       <c r="C54" t="str">
         <v>206 Book Transfer Credit</v>
@@ -1383,7 +1383,7 @@
         <v>06/30/2025</v>
       </c>
       <c r="B55" t="str">
-        <v>$976.36</v>
+        <v>$29,479.49</v>
       </c>
       <c r="C55" t="str">
         <v>206 Book Transfer Credit</v>
@@ -1448,7 +1448,7 @@
         <v>06/04/2025</v>
       </c>
       <c r="B2" t="str">
-        <v>$23,138.05</v>
+        <v>$2,019.00</v>
       </c>
       <c r="C2" t="str">
         <v>165 Preauthorized ACH Credit</v>
@@ -1465,7 +1465,7 @@
         <v>06/04/2025</v>
       </c>
       <c r="B3" t="str">
-        <v>$2,019.00</v>
+        <v>$23,138.05</v>
       </c>
       <c r="C3" t="str">
         <v>165 Preauthorized ACH Credit</v>
@@ -1747,16 +1747,16 @@
         <v>06/01/2025</v>
       </c>
       <c r="B3" t="str">
-        <v>06/02/2025</v>
+        <v>06/03/2025</v>
       </c>
       <c r="C3" t="str">
-        <v>$2,842.69</v>
+        <v>$522.34</v>
       </c>
       <c r="D3" t="str">
-        <v>$2,842.69</v>
+        <v>$522.34</v>
       </c>
       <c r="E3" t="str">
-        <v>Humana 05/28/2025</v>
+        <v>HUMANA INC. 05/29/2025</v>
       </c>
       <c r="F3" t="str">
         <v>HMPHCCLAIMPMT TRN***\LADY LAKE SPECIALTY CA</v>
@@ -1773,13 +1773,13 @@
         <v>06/03/2025</v>
       </c>
       <c r="C4" t="str">
-        <v>$522.34</v>
+        <v>$609.10</v>
       </c>
       <c r="D4" t="str">
-        <v>$522.34</v>
+        <v>$609.10</v>
       </c>
       <c r="E4" t="str">
-        <v>HUMANA INC. 05/29/2025</v>
+        <v>HUMANA INC. 05/31/2025</v>
       </c>
       <c r="F4" t="str">
         <v>HMPHCCLAIMPMT TRN***\LADY LAKE SPECIALTY CA</v>
@@ -1793,16 +1793,16 @@
         <v>06/01/2025</v>
       </c>
       <c r="B5" t="str">
-        <v>06/03/2025</v>
+        <v>06/02/2025</v>
       </c>
       <c r="C5" t="str">
-        <v>$609.10</v>
+        <v>$2,842.69</v>
       </c>
       <c r="D5" t="str">
-        <v>$609.10</v>
+        <v>$2,842.69</v>
       </c>
       <c r="E5" t="str">
-        <v>HUMANA INC. 05/31/2025</v>
+        <v>Humana 05/28/2025</v>
       </c>
       <c r="F5" t="str">
         <v>HMPHCCLAIMPMT TRN***\LADY LAKE SPECIALTY CA</v>
@@ -1834,53 +1834,53 @@
         <v>Exact</v>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7" t="str" xml:space="preserve">
+    <row r="7">
+      <c r="A7" t="str">
+        <v>06/02/2025</v>
+      </c>
+      <c r="B7" t="str">
+        <v>06/05/2025</v>
+      </c>
+      <c r="C7" t="str">
+        <v>$915.78</v>
+      </c>
+      <c r="D7" t="str">
+        <v>$915.78</v>
+      </c>
+      <c r="E7" t="str">
+        <v>HUMANA INC. 06/02/2025</v>
+      </c>
+      <c r="F7" t="str">
+        <v>HMPHCCLAIMPMT TRN***\LADY LAKE SPECIALTY CA</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str" xml:space="preserve">
         <v xml:space="preserve">06/02/2025
 -
 06/05/2025</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B8" t="str">
         <v>06/06/2025</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C8" t="str">
         <v>$1,880.00</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D8" t="str">
         <v>$1,880.00</v>
       </c>
-      <c r="E7" t="str" xml:space="preserve">
+      <c r="E8" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $470.00 (Wellmed VCC 06/02/2025 | 6/2)
 2: $1,410.00 (Wellmed VCC 06/05/2025 | 6/5)</v>
       </c>
-      <c r="F7" t="str">
+      <c r="F8" t="str">
         <v>BANKCARDBTOT DEP</v>
       </c>
-      <c r="G7" t="str">
+      <c r="G8" t="str">
         <v>Many-to-One</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>06/02/2025</v>
-      </c>
-      <c r="B8" t="str">
-        <v>06/05/2025</v>
-      </c>
-      <c r="C8" t="str">
-        <v>$915.78</v>
-      </c>
-      <c r="D8" t="str">
-        <v>$915.78</v>
-      </c>
-      <c r="E8" t="str">
-        <v>HUMANA INC. 06/02/2025</v>
-      </c>
-      <c r="F8" t="str">
-        <v>HMPHCCLAIMPMT TRN***\LADY LAKE SPECIALTY CA</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Exact</v>
       </c>
     </row>
     <row r="9">
@@ -1911,19 +1911,19 @@
         <v>06/02/2025</v>
       </c>
       <c r="B10" t="str">
-        <v>06/02/2025</v>
+        <v>06/03/2025</v>
       </c>
       <c r="C10" t="str">
-        <v>$6,646.71</v>
+        <v>$6,113.09</v>
       </c>
       <c r="D10" t="str">
-        <v>$6,646.71</v>
+        <v>$6,113.09</v>
       </c>
       <c r="E10" t="str">
-        <v>Deposit 06/02/2025</v>
+        <v>WPS GHA - MAC J5 PART A 06/02/2025</v>
       </c>
       <c r="F10" t="str">
-        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
+        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G10" t="str">
         <v>Exact</v>
@@ -1934,19 +1934,19 @@
         <v>06/02/2025</v>
       </c>
       <c r="B11" t="str">
-        <v>06/03/2025</v>
+        <v>06/02/2025</v>
       </c>
       <c r="C11" t="str">
-        <v>$6,113.09</v>
+        <v>$6,646.71</v>
       </c>
       <c r="D11" t="str">
-        <v>$6,113.09</v>
+        <v>$6,646.71</v>
       </c>
       <c r="E11" t="str">
-        <v>WPS GHA - MAC J5 PART A 06/02/2025</v>
+        <v>Deposit 06/02/2025</v>
       </c>
       <c r="F11" t="str">
-        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~LADY LAKE SPECIALTY CA</v>
+        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
       </c>
       <c r="G11" t="str">
         <v>Exact</v>
@@ -1960,16 +1960,16 @@
         <v>06/03/2025</v>
       </c>
       <c r="C12" t="str">
-        <v>$15,900.00</v>
+        <v>$2,019.00</v>
       </c>
       <c r="D12" t="str">
-        <v>$15,900.00</v>
+        <v>$2,019.00</v>
       </c>
       <c r="E12" t="str">
-        <v>CAREPLUS HEALTH PLANS,INC 06/03/2025</v>
+        <v>RFMS 06/03/2025</v>
       </c>
       <c r="F12" t="str">
-        <v>HUMANA INC US LEHCCLAIMPMT TRN***\LADY LAKE NH LLC DBA</v>
+        <v>NATL DATACARE CRT# DIRECT DEPOSIT</v>
       </c>
       <c r="G12" t="str">
         <v>Exact</v>
@@ -1983,16 +1983,16 @@
         <v>06/03/2025</v>
       </c>
       <c r="C13" t="str">
-        <v>$44,998.49</v>
+        <v>$8,932.50</v>
       </c>
       <c r="D13" t="str">
-        <v>$44,998.49</v>
+        <v>$8,932.50</v>
       </c>
       <c r="E13" t="str">
         <v>Deposit 06/03/2025</v>
       </c>
       <c r="F13" t="str">
-        <v>LADY LAKE SPECIASETTLEMENT</v>
+        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
       </c>
       <c r="G13" t="str">
         <v>Exact</v>
@@ -2003,19 +2003,19 @@
         <v>06/03/2025</v>
       </c>
       <c r="B14" t="str">
-        <v>06/03/2025</v>
+        <v>06/04/2025</v>
       </c>
       <c r="C14" t="str">
-        <v>$8,932.50</v>
+        <v>$9,657.18</v>
       </c>
       <c r="D14" t="str">
-        <v>$8,932.50</v>
+        <v>$9,657.18</v>
       </c>
       <c r="E14" t="str">
-        <v>Deposit 06/03/2025</v>
+        <v>SUNSHINE HEALTH 06/03/2025</v>
       </c>
       <c r="F14" t="str">
-        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
+        <v>SUNSHINE STATE HHCCLAIMPMTTRN***\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G14" t="str">
         <v>Exact</v>
@@ -2029,16 +2029,16 @@
         <v>06/03/2025</v>
       </c>
       <c r="C15" t="str">
-        <v>$2,019.00</v>
+        <v>$15,900.00</v>
       </c>
       <c r="D15" t="str">
-        <v>$2,019.00</v>
+        <v>$15,900.00</v>
       </c>
       <c r="E15" t="str">
-        <v>RFMS 06/03/2025</v>
+        <v>CAREPLUS HEALTH PLANS,INC 06/03/2025</v>
       </c>
       <c r="F15" t="str">
-        <v>NATL DATACARE CRT# DIRECT DEPOSIT</v>
+        <v>HUMANA INC US LEHCCLAIMPMT TRN***\LADY LAKE NH LLC DBA</v>
       </c>
       <c r="G15" t="str">
         <v>Exact</v>
@@ -2072,19 +2072,19 @@
         <v>06/03/2025</v>
       </c>
       <c r="B17" t="str">
-        <v>06/04/2025</v>
+        <v>06/03/2025</v>
       </c>
       <c r="C17" t="str">
-        <v>$9,657.18</v>
+        <v>$44,998.49</v>
       </c>
       <c r="D17" t="str">
-        <v>$9,657.18</v>
+        <v>$44,998.49</v>
       </c>
       <c r="E17" t="str">
-        <v>SUNSHINE HEALTH 06/03/2025</v>
+        <v>Deposit 06/03/2025</v>
       </c>
       <c r="F17" t="str">
-        <v>SUNSHINE STATE HHCCLAIMPMTTRN***\LADY LAKE SPECIALTY CA</v>
+        <v>LADY LAKE SPECIASETTLEMENT</v>
       </c>
       <c r="G17" t="str">
         <v>Exact</v>
@@ -2118,19 +2118,19 @@
         <v>06/04/2025</v>
       </c>
       <c r="B19" t="str">
-        <v>06/09/2025</v>
+        <v>06/04/2025</v>
       </c>
       <c r="C19" t="str">
-        <v>$102,987.03</v>
+        <v>$568.10</v>
       </c>
       <c r="D19" t="str">
-        <v>$102,987.03</v>
+        <v>$568.10</v>
       </c>
       <c r="E19" t="str">
-        <v>HUMANA INC. 06/04/2025</v>
+        <v>UNITEDHEALTHCARE COMMUNITY PLAN 06/04/2025</v>
       </c>
       <c r="F19" t="str">
-        <v>HMPHCCLAIMPMT TRN***\LADY LAKE SPECIALTY CA</v>
+        <v>UHC COMMUNITY PLHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G19" t="str">
         <v>Exact</v>
@@ -2144,16 +2144,16 @@
         <v>06/04/2025</v>
       </c>
       <c r="C20" t="str">
-        <v>$5,909.75</v>
+        <v>$807.00</v>
       </c>
       <c r="D20" t="str">
-        <v>$5,909.75</v>
+        <v>$807.00</v>
       </c>
       <c r="E20" t="str">
-        <v>Deposit 06/04/2025</v>
+        <v>RFMS 06/04/2025</v>
       </c>
       <c r="F20" t="str">
-        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
+        <v>NATL DATACARE CRT#A DEP RECORD #D</v>
       </c>
       <c r="G20" t="str">
         <v>Exact</v>
@@ -2167,16 +2167,16 @@
         <v>06/04/2025</v>
       </c>
       <c r="C21" t="str">
-        <v>$807.00</v>
+        <v>$5,909.75</v>
       </c>
       <c r="D21" t="str">
-        <v>$807.00</v>
+        <v>$5,909.75</v>
       </c>
       <c r="E21" t="str">
-        <v>RFMS 06/04/2025</v>
+        <v>Deposit 06/04/2025</v>
       </c>
       <c r="F21" t="str">
-        <v>NATL DATACARE CRT#A DEP RECORD #D</v>
+        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
       </c>
       <c r="G21" t="str">
         <v>Exact</v>
@@ -2187,19 +2187,19 @@
         <v>06/04/2025</v>
       </c>
       <c r="B22" t="str">
-        <v>06/04/2025</v>
+        <v>06/05/2025</v>
       </c>
       <c r="C22" t="str">
-        <v>$568.10</v>
+        <v>$25,710.00</v>
       </c>
       <c r="D22" t="str">
-        <v>$568.10</v>
+        <v>$25,710.00</v>
       </c>
       <c r="E22" t="str">
-        <v>UNITEDHEALTHCARE COMMUNITY PLAN 06/04/2025</v>
+        <v>WPS GHA - MAC J5 PART A 06/04/2025</v>
       </c>
       <c r="F22" t="str">
-        <v>UHC COMMUNITY PLHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
+        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G22" t="str">
         <v>Exact</v>
@@ -2210,19 +2210,19 @@
         <v>06/04/2025</v>
       </c>
       <c r="B23" t="str">
-        <v>06/05/2025</v>
+        <v>06/09/2025</v>
       </c>
       <c r="C23" t="str">
-        <v>$25,710.00</v>
+        <v>$102,987.03</v>
       </c>
       <c r="D23" t="str">
-        <v>$25,710.00</v>
+        <v>$102,987.03</v>
       </c>
       <c r="E23" t="str">
-        <v>WPS GHA - MAC J5 PART A 06/04/2025</v>
+        <v>HUMANA INC. 06/04/2025</v>
       </c>
       <c r="F23" t="str">
-        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~LADY LAKE SPECIALTY CA</v>
+        <v>HMPHCCLAIMPMT TRN***\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G23" t="str">
         <v>Exact</v>
@@ -2259,16 +2259,16 @@
         <v>06/05/2025</v>
       </c>
       <c r="C25" t="str">
-        <v>$19,060.00</v>
+        <v>$2,003.00</v>
       </c>
       <c r="D25" t="str">
-        <v>$19,060.00</v>
+        <v>$2,003.00</v>
       </c>
       <c r="E25" t="str">
-        <v>Freedom Health 06/03/2025</v>
+        <v>Deposit 06/05/2025</v>
       </c>
       <c r="F25" t="str">
-        <v>FH MEDICARE HAXHCCLAIMPMTTRN***\LADY LAKE SPECIALTY CA</v>
+        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
       </c>
       <c r="G25" t="str">
         <v>Exact</v>
@@ -2282,16 +2282,16 @@
         <v>06/05/2025</v>
       </c>
       <c r="C26" t="str">
-        <v>$2,003.00</v>
+        <v>$14,679.92</v>
       </c>
       <c r="D26" t="str">
-        <v>$2,003.00</v>
+        <v>$14,679.92</v>
       </c>
       <c r="E26" t="str">
-        <v>Deposit 06/05/2025</v>
+        <v>UNITED HEALTHCARE INSURANCE COMPANY 06/05/ 2025</v>
       </c>
       <c r="F26" t="str">
-        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
+        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**T**\LADYLAKE SPECIALTY CA</v>
       </c>
       <c r="G26" t="str">
         <v>Exact</v>
@@ -2305,16 +2305,16 @@
         <v>06/05/2025</v>
       </c>
       <c r="C27" t="str">
-        <v>$14,679.92</v>
+        <v>$19,060.00</v>
       </c>
       <c r="D27" t="str">
-        <v>$14,679.92</v>
+        <v>$19,060.00</v>
       </c>
       <c r="E27" t="str">
-        <v>UNITED HEALTHCARE INSURANCE COMPANY 06/05/ 2025</v>
+        <v>Freedom Health 06/03/2025</v>
       </c>
       <c r="F27" t="str">
-        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**T**\LADYLAKE SPECIALTY CA</v>
+        <v>FH MEDICARE HAXHCCLAIMPMTTRN***\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G27" t="str">
         <v>Exact</v>
@@ -2325,19 +2325,19 @@
         <v>06/06/2025</v>
       </c>
       <c r="B28" t="str">
-        <v>06/09/2025</v>
+        <v>06/06/2025</v>
       </c>
       <c r="C28" t="str">
-        <v>$8,648.07</v>
+        <v>$300.00</v>
       </c>
       <c r="D28" t="str">
-        <v>$8,648.07</v>
+        <v>$300.00</v>
       </c>
       <c r="E28" t="str">
-        <v>AETNA BETTER HEALTH OF FLORIDA 06/06/2025</v>
+        <v>UNITED HEALTHCARE INSURANCE COMPANY 06/06/ 2025</v>
       </c>
       <c r="F28" t="str">
-        <v>HNB - ECHOHCCLAIMPMT TRN***\LADY LAKE SPECIALTY CA</v>
+        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**T**\LADYLAKE SPECIALTY CA</v>
       </c>
       <c r="G28" t="str">
         <v>Exact</v>
@@ -2351,16 +2351,16 @@
         <v>06/06/2025</v>
       </c>
       <c r="C29" t="str">
-        <v>$13,364.21</v>
+        <v>$379.64</v>
       </c>
       <c r="D29" t="str">
-        <v>$13,364.21</v>
+        <v>$379.64</v>
       </c>
       <c r="E29" t="str">
-        <v>Deposit 06/06/2025</v>
+        <v>WPS GHA - MAC J5 PART A 06/05/2025</v>
       </c>
       <c r="F29" t="str">
-        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
+        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G29" t="str">
         <v>Exact</v>
@@ -2374,16 +2374,16 @@
         <v>06/09/2025</v>
       </c>
       <c r="C30" t="str">
-        <v>$80,549.41</v>
+        <v>$8,648.07</v>
       </c>
       <c r="D30" t="str">
-        <v>$80,549.41</v>
+        <v>$8,648.07</v>
       </c>
       <c r="E30" t="str">
-        <v>SUNSHINE HEALTH 06/06/2025</v>
+        <v>AETNA BETTER HEALTH OF FLORIDA 06/06/2025</v>
       </c>
       <c r="F30" t="str">
-        <v>SUNSHINE STATE HHCCLAIMPMTTRN***\LADY LAKE SPECIALTY CA</v>
+        <v>HNB - ECHOHCCLAIMPMT TRN***\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G30" t="str">
         <v>Exact</v>
@@ -2397,16 +2397,16 @@
         <v>06/06/2025</v>
       </c>
       <c r="C31" t="str">
-        <v>$300.00</v>
+        <v>$13,364.21</v>
       </c>
       <c r="D31" t="str">
-        <v>$300.00</v>
+        <v>$13,364.21</v>
       </c>
       <c r="E31" t="str">
-        <v>UNITED HEALTHCARE INSURANCE COMPANY 06/06/ 2025</v>
+        <v>Deposit 06/06/2025</v>
       </c>
       <c r="F31" t="str">
-        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**T**\LADYLAKE SPECIALTY CA</v>
+        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
       </c>
       <c r="G31" t="str">
         <v>Exact</v>
@@ -2417,19 +2417,19 @@
         <v>06/06/2025</v>
       </c>
       <c r="B32" t="str">
-        <v>06/06/2025</v>
+        <v>06/09/2025</v>
       </c>
       <c r="C32" t="str">
-        <v>$379.64</v>
+        <v>$80,549.41</v>
       </c>
       <c r="D32" t="str">
-        <v>$379.64</v>
+        <v>$80,549.41</v>
       </c>
       <c r="E32" t="str">
-        <v>WPS GHA - MAC J5 PART A 06/05/2025</v>
+        <v>SUNSHINE HEALTH 06/06/2025</v>
       </c>
       <c r="F32" t="str">
-        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~LADY LAKE SPECIALTY CA</v>
+        <v>SUNSHINE STATE HHCCLAIMPMTTRN***\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G32" t="str">
         <v>Exact</v>
@@ -2443,16 +2443,16 @@
         <v>06/09/2025</v>
       </c>
       <c r="C33" t="str">
-        <v>$3,730.00</v>
+        <v>$203.17</v>
       </c>
       <c r="D33" t="str">
-        <v>$3,730.00</v>
+        <v>$203.17</v>
       </c>
       <c r="E33" t="str">
-        <v>RFMS 06/09/2025</v>
+        <v>UNITEDHEALTHCARE 06/09/2025</v>
       </c>
       <c r="F33" t="str">
-        <v>NATL DATACARE CRT# DIRECT DEPOSIT</v>
+        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G33" t="str">
         <v>Exact</v>
@@ -2466,16 +2466,16 @@
         <v>06/09/2025</v>
       </c>
       <c r="C34" t="str">
-        <v>$7,399.60</v>
+        <v>$3,730.00</v>
       </c>
       <c r="D34" t="str">
-        <v>$7,399.60</v>
+        <v>$3,730.00</v>
       </c>
       <c r="E34" t="str">
-        <v>SUNSHINE HEALTH 06/09/2025</v>
+        <v>RFMS 06/09/2025</v>
       </c>
       <c r="F34" t="str">
-        <v>SUNSHINE STATE HHCCLAIMPMTTRN***\LADY LAKE SPECIALTY CA</v>
+        <v>NATL DATACARE CRT# DIRECT DEPOSIT</v>
       </c>
       <c r="G34" t="str">
         <v>Exact</v>
@@ -2489,16 +2489,16 @@
         <v>06/09/2025</v>
       </c>
       <c r="C35" t="str">
-        <v>$167,823.80</v>
+        <v>$7,399.60</v>
       </c>
       <c r="D35" t="str">
-        <v>$167,823.80</v>
+        <v>$7,399.60</v>
       </c>
       <c r="E35" t="str">
-        <v>VA 06/09/2025</v>
+        <v>SUNSHINE HEALTH 06/09/2025</v>
       </c>
       <c r="F35" t="str">
-        <v>TREAS MISC PAY ISA*****ZZ*US TREASURY *ZZ*VENDORPAYMENTS**LADY LAKE NH LLC</v>
+        <v>SUNSHINE STATE HHCCLAIMPMTTRN***\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G35" t="str">
         <v>Exact</v>
@@ -2512,16 +2512,16 @@
         <v>06/09/2025</v>
       </c>
       <c r="C36" t="str">
-        <v>$203.17</v>
+        <v>$167,823.80</v>
       </c>
       <c r="D36" t="str">
-        <v>$203.17</v>
+        <v>$167,823.80</v>
       </c>
       <c r="E36" t="str">
-        <v>UNITEDHEALTHCARE 06/09/2025</v>
+        <v>VA 06/09/2025</v>
       </c>
       <c r="F36" t="str">
-        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
+        <v>TREAS MISC PAY ISA*****ZZ*US TREASURY *ZZ*VENDORPAYMENTS**LADY LAKE NH LLC</v>
       </c>
       <c r="G36" t="str">
         <v>Exact</v>
@@ -2555,19 +2555,19 @@
         <v>06/10/2025</v>
       </c>
       <c r="B38" t="str">
-        <v>06/10/2025</v>
+        <v>06/11/2025</v>
       </c>
       <c r="C38" t="str">
-        <v>$18,232.78</v>
+        <v>$3,806.55</v>
       </c>
       <c r="D38" t="str">
-        <v>$18,232.78</v>
+        <v>$3,806.55</v>
       </c>
       <c r="E38" t="str">
-        <v>VA 06/10/2025</v>
+        <v>WPS GHA - MAC J5 PART A 06/10/2025</v>
       </c>
       <c r="F38" t="str">
-        <v>TREAS MISC PAY ISA*****ZZ*US TREASURY *ZZ*VENDORPAYMENTS**LADY LAKE NH LLC</v>
+        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G38" t="str">
         <v>Exact</v>
@@ -2578,19 +2578,19 @@
         <v>06/10/2025</v>
       </c>
       <c r="B39" t="str">
-        <v>06/11/2025</v>
+        <v>06/10/2025</v>
       </c>
       <c r="C39" t="str">
-        <v>$3,806.55</v>
+        <v>$18,232.78</v>
       </c>
       <c r="D39" t="str">
-        <v>$3,806.55</v>
+        <v>$18,232.78</v>
       </c>
       <c r="E39" t="str">
-        <v>WPS GHA - MAC J5 PART A 06/10/2025</v>
+        <v>VA 06/10/2025</v>
       </c>
       <c r="F39" t="str">
-        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~LADY LAKE SPECIALTY CA</v>
+        <v>TREAS MISC PAY ISA*****ZZ*US TREASURY *ZZ*VENDORPAYMENTS**LADY LAKE NH LLC</v>
       </c>
       <c r="G39" t="str">
         <v>Exact</v>
@@ -2601,19 +2601,19 @@
         <v>06/11/2025</v>
       </c>
       <c r="B40" t="str">
-        <v>06/16/2025</v>
+        <v>06/11/2025</v>
       </c>
       <c r="C40" t="str">
-        <v>$7,373.07</v>
+        <v>$2,649.95</v>
       </c>
       <c r="D40" t="str">
-        <v>$7,373.07</v>
+        <v>$2,649.95</v>
       </c>
       <c r="E40" t="str">
-        <v>HUMANA INC. 06/11/2025</v>
+        <v>Deposit 06/11/2025</v>
       </c>
       <c r="F40" t="str">
-        <v>HMPHCCLAIMPMT TRN***\LADY LAKE SPECIALTY CA</v>
+        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
       </c>
       <c r="G40" t="str">
         <v>Exact</v>
@@ -2624,16 +2624,16 @@
         <v>06/11/2025</v>
       </c>
       <c r="B41" t="str">
-        <v>06/11/2025</v>
+        <v>06/12/2025</v>
       </c>
       <c r="C41" t="str">
-        <v>$2,649.95</v>
+        <v>$3,830.29</v>
       </c>
       <c r="D41" t="str">
-        <v>$2,649.95</v>
+        <v>$3,830.29</v>
       </c>
       <c r="E41" t="str">
-        <v>Deposit 06/11/2025</v>
+        <v>Credit Card 06/11/2025</v>
       </c>
       <c r="F41" t="str">
         <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
@@ -2647,19 +2647,19 @@
         <v>06/11/2025</v>
       </c>
       <c r="B42" t="str">
-        <v>06/12/2025</v>
+        <v>06/16/2025</v>
       </c>
       <c r="C42" t="str">
-        <v>$3,830.29</v>
+        <v>$7,373.07</v>
       </c>
       <c r="D42" t="str">
-        <v>$3,830.29</v>
+        <v>$7,373.07</v>
       </c>
       <c r="E42" t="str">
-        <v>Credit Card 06/11/2025</v>
+        <v>HUMANA INC. 06/11/2025</v>
       </c>
       <c r="F42" t="str">
-        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
+        <v>HMPHCCLAIMPMT TRN***\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G42" t="str">
         <v>Exact</v>
@@ -2673,16 +2673,16 @@
         <v>06/11/2025</v>
       </c>
       <c r="C43" t="str">
-        <v>$87,174.76</v>
+        <v>$13,583.47</v>
       </c>
       <c r="D43" t="str">
-        <v>$87,174.76</v>
+        <v>$13,583.47</v>
       </c>
       <c r="E43" t="str">
-        <v>UNITEDHEALTHCARE COMMUNITY PLAN 06/11/2025</v>
+        <v>UNITEDHEALTHCARE 06/11/2025</v>
       </c>
       <c r="F43" t="str">
-        <v>UHC COMMUNITY PLHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
+        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G43" t="str">
         <v>Exact</v>
@@ -2693,19 +2693,19 @@
         <v>06/11/2025</v>
       </c>
       <c r="B44" t="str">
-        <v>06/11/2025</v>
+        <v>06/12/2025</v>
       </c>
       <c r="C44" t="str">
-        <v>$35,520.58</v>
+        <v>$28,439.88</v>
       </c>
       <c r="D44" t="str">
-        <v>$35,520.58</v>
+        <v>$28,439.88</v>
       </c>
       <c r="E44" t="str">
-        <v>UNITEDHEALTHCARE COMMUNITY PLAN 06/11/2025</v>
+        <v>WPS GHA - MAC J5 PART A 06/11/2025</v>
       </c>
       <c r="F44" t="str">
-        <v>UHC COMMUNITY PLHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
+        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G44" t="str">
         <v>Exact</v>
@@ -2719,16 +2719,16 @@
         <v>06/11/2025</v>
       </c>
       <c r="C45" t="str">
-        <v>$13,583.47</v>
+        <v>$35,520.58</v>
       </c>
       <c r="D45" t="str">
-        <v>$13,583.47</v>
+        <v>$35,520.58</v>
       </c>
       <c r="E45" t="str">
-        <v>UNITEDHEALTHCARE 06/11/2025</v>
+        <v>UNITEDHEALTHCARE COMMUNITY PLAN 06/11/2025</v>
       </c>
       <c r="F45" t="str">
-        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
+        <v>UHC COMMUNITY PLHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G45" t="str">
         <v>Exact</v>
@@ -2739,19 +2739,19 @@
         <v>06/11/2025</v>
       </c>
       <c r="B46" t="str">
-        <v>06/12/2025</v>
+        <v>06/11/2025</v>
       </c>
       <c r="C46" t="str">
-        <v>$28,439.88</v>
+        <v>$87,174.76</v>
       </c>
       <c r="D46" t="str">
-        <v>$28,439.88</v>
+        <v>$87,174.76</v>
       </c>
       <c r="E46" t="str">
-        <v>WPS GHA - MAC J5 PART A 06/11/2025</v>
+        <v>UNITEDHEALTHCARE COMMUNITY PLAN 06/11/2025</v>
       </c>
       <c r="F46" t="str">
-        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~LADY LAKE SPECIALTY CA</v>
+        <v>UHC COMMUNITY PLHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G46" t="str">
         <v>Exact</v>
@@ -2792,16 +2792,16 @@
         <v>06/13/2025</v>
       </c>
       <c r="C48" t="str">
-        <v>$25,383.01</v>
+        <v>$21,634.45</v>
       </c>
       <c r="D48" t="str">
-        <v>$25,383.01</v>
+        <v>$21,634.45</v>
       </c>
       <c r="E48" t="str">
-        <v>VA 06/13/2025</v>
+        <v>UNITEDHEALTHCARE COMMUNITY PLAN 06/13/2025</v>
       </c>
       <c r="F48" t="str">
-        <v>TREAS MISC PAY ISA*****ZZ*US TREASURY *ZZ*VENDORPAYMENTS**LADY LAKE NH LLC</v>
+        <v>UHC COMMUNITY PLHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G48" t="str">
         <v>Exact</v>
@@ -2815,16 +2815,16 @@
         <v>06/13/2025</v>
       </c>
       <c r="C49" t="str">
-        <v>$21,634.45</v>
+        <v>$25,383.01</v>
       </c>
       <c r="D49" t="str">
-        <v>$21,634.45</v>
+        <v>$25,383.01</v>
       </c>
       <c r="E49" t="str">
-        <v>UNITEDHEALTHCARE COMMUNITY PLAN 06/13/2025</v>
+        <v>VA 06/13/2025</v>
       </c>
       <c r="F49" t="str">
-        <v>UHC COMMUNITY PLHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
+        <v>TREAS MISC PAY ISA*****ZZ*US TREASURY *ZZ*VENDORPAYMENTS**LADY LAKE NH LLC</v>
       </c>
       <c r="G49" t="str">
         <v>Exact</v>
@@ -2835,19 +2835,19 @@
         <v>06/16/2025</v>
       </c>
       <c r="B50" t="str">
-        <v>06/16/2025</v>
+        <v>06/17/2025</v>
       </c>
       <c r="C50" t="str">
-        <v>$725.12</v>
+        <v>$466.99</v>
       </c>
       <c r="D50" t="str">
-        <v>$725.12</v>
+        <v>$466.99</v>
       </c>
       <c r="E50" t="str">
-        <v>Credit Card 06/13/2025</v>
+        <v>WPS GHA - MAC J5 PART A 06/16/2025</v>
       </c>
       <c r="F50" t="str">
-        <v>BANKCARDBTOT DEP</v>
+        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G50" t="str">
         <v>Exact</v>
@@ -2861,16 +2861,16 @@
         <v>06/16/2025</v>
       </c>
       <c r="C51" t="str">
-        <v>$143,276.14</v>
+        <v>$725.12</v>
       </c>
       <c r="D51" t="str">
-        <v>$143,276.14</v>
+        <v>$725.12</v>
       </c>
       <c r="E51" t="str">
-        <v>Deposit 06/16/2025</v>
+        <v>Credit Card 06/13/2025</v>
       </c>
       <c r="F51" t="str">
-        <v>LADY LAKE SPECIASETTLEMENT</v>
+        <v>BANKCARDBTOT DEP</v>
       </c>
       <c r="G51" t="str">
         <v>Exact</v>
@@ -2884,16 +2884,16 @@
         <v>06/16/2025</v>
       </c>
       <c r="C52" t="str">
-        <v>$35,219.31</v>
+        <v>$7,104.07</v>
       </c>
       <c r="D52" t="str">
-        <v>$35,219.31</v>
+        <v>$7,104.07</v>
       </c>
       <c r="E52" t="str">
-        <v>Deposit 06/16/2025</v>
+        <v>SUNSHINE HEALTH 06/13/2025</v>
       </c>
       <c r="F52" t="str">
-        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
+        <v>SUNSHINE STATE HHCCLAIMPMTTRN***\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G52" t="str">
         <v>Exact</v>
@@ -2907,16 +2907,16 @@
         <v>06/16/2025</v>
       </c>
       <c r="C53" t="str">
-        <v>$11,900.43</v>
+        <v>$8,004.07</v>
       </c>
       <c r="D53" t="str">
-        <v>$11,900.43</v>
+        <v>$8,004.07</v>
       </c>
       <c r="E53" t="str">
-        <v>SUNSHINE HEALTH 06/16/2025</v>
+        <v>UNITEDHEALTHCARE 06/16/2025</v>
       </c>
       <c r="F53" t="str">
-        <v>SUNSHINE STATE HHCCLAIMPMTTRN***\LADY LAKE SPECIALTY CA</v>
+        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G53" t="str">
         <v>Exact</v>
@@ -2930,13 +2930,13 @@
         <v>06/16/2025</v>
       </c>
       <c r="C54" t="str">
-        <v>$7,104.07</v>
+        <v>$11,900.43</v>
       </c>
       <c r="D54" t="str">
-        <v>$7,104.07</v>
+        <v>$11,900.43</v>
       </c>
       <c r="E54" t="str">
-        <v>SUNSHINE HEALTH 06/13/2025</v>
+        <v>SUNSHINE HEALTH 06/16/2025</v>
       </c>
       <c r="F54" t="str">
         <v>SUNSHINE STATE HHCCLAIMPMTTRN***\LADY LAKE SPECIALTY CA</v>
@@ -2953,16 +2953,16 @@
         <v>06/16/2025</v>
       </c>
       <c r="C55" t="str">
-        <v>$50,505.52</v>
+        <v>$35,219.31</v>
       </c>
       <c r="D55" t="str">
-        <v>$50,505.52</v>
+        <v>$35,219.31</v>
       </c>
       <c r="E55" t="str">
-        <v>VA 06/16/2025</v>
+        <v>Deposit 06/16/2025</v>
       </c>
       <c r="F55" t="str">
-        <v>TREAS MISC PAY ISA*****ZZ*US TREASURY *ZZ*VENDORPAYMENTS**LADY LAKE NH LLC</v>
+        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
       </c>
       <c r="G55" t="str">
         <v>Exact</v>
@@ -2976,16 +2976,16 @@
         <v>06/16/2025</v>
       </c>
       <c r="C56" t="str">
-        <v>$8,004.07</v>
+        <v>$50,505.52</v>
       </c>
       <c r="D56" t="str">
-        <v>$8,004.07</v>
+        <v>$50,505.52</v>
       </c>
       <c r="E56" t="str">
-        <v>UNITEDHEALTHCARE 06/16/2025</v>
+        <v>VA 06/16/2025</v>
       </c>
       <c r="F56" t="str">
-        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
+        <v>TREAS MISC PAY ISA*****ZZ*US TREASURY *ZZ*VENDORPAYMENTS**LADY LAKE NH LLC</v>
       </c>
       <c r="G56" t="str">
         <v>Exact</v>
@@ -2996,19 +2996,19 @@
         <v>06/16/2025</v>
       </c>
       <c r="B57" t="str">
-        <v>06/17/2025</v>
+        <v>06/16/2025</v>
       </c>
       <c r="C57" t="str">
-        <v>$466.99</v>
+        <v>$143,276.14</v>
       </c>
       <c r="D57" t="str">
-        <v>$466.99</v>
+        <v>$143,276.14</v>
       </c>
       <c r="E57" t="str">
-        <v>WPS GHA - MAC J5 PART A 06/16/2025</v>
+        <v>Deposit 06/16/2025</v>
       </c>
       <c r="F57" t="str">
-        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~LADY LAKE SPECIALTY CA</v>
+        <v>LADY LAKE SPECIASETTLEMENT</v>
       </c>
       <c r="G57" t="str">
         <v>Exact</v>
@@ -3019,19 +3019,19 @@
         <v>06/17/2025</v>
       </c>
       <c r="B58" t="str">
-        <v>06/18/2025</v>
+        <v>06/17/2025</v>
       </c>
       <c r="C58" t="str">
-        <v>$9,300.00</v>
+        <v>$3,290.00</v>
       </c>
       <c r="D58" t="str">
-        <v>$9,300.00</v>
+        <v>$3,290.00</v>
       </c>
       <c r="E58" t="str">
-        <v>AMBETTER 06/17/2025</v>
+        <v>UNITED HEALTHCARE INSURANCE COMPANY 06/17/ 2025</v>
       </c>
       <c r="F58" t="str">
-        <v>MARKETPLACEHCCLAIMPMTTRN***\LADY LAKE SPECIALTY CA</v>
+        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**T**\LADYLAKE SPECIALTY CA</v>
       </c>
       <c r="G58" t="str">
         <v>Exact</v>
@@ -3065,19 +3065,19 @@
         <v>06/17/2025</v>
       </c>
       <c r="B60" t="str">
-        <v>06/17/2025</v>
+        <v>06/18/2025</v>
       </c>
       <c r="C60" t="str">
-        <v>$3,290.00</v>
+        <v>$9,300.00</v>
       </c>
       <c r="D60" t="str">
-        <v>$3,290.00</v>
+        <v>$9,300.00</v>
       </c>
       <c r="E60" t="str">
-        <v>UNITED HEALTHCARE INSURANCE COMPANY 06/17/ 2025</v>
+        <v>AMBETTER 06/17/2025</v>
       </c>
       <c r="F60" t="str">
-        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**T**\LADYLAKE SPECIALTY CA</v>
+        <v>MARKETPLACEHCCLAIMPMTTRN***\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G60" t="str">
         <v>Exact</v>
@@ -3088,71 +3088,71 @@
         <v>06/18/2025</v>
       </c>
       <c r="B61" t="str">
-        <v>06/20/2025</v>
+        <v>06/18/2025</v>
       </c>
       <c r="C61" t="str">
-        <v>$21,089.63</v>
+        <v>$818.00</v>
       </c>
       <c r="D61" t="str">
-        <v>$21,089.63</v>
+        <v>$818.00</v>
       </c>
       <c r="E61" t="str">
-        <v>STATE OF FLORIDA MEDICAID 06/18/2025</v>
+        <v>RFMS 06/18/2025</v>
       </c>
       <c r="F61" t="str">
-        <v>ACH MEDICAIDHCCLAIMPMT TRN***~LADY LAKE SPECIALTY CA</v>
+        <v>NATL DATACARE CRT#A DEP RECORD #D</v>
       </c>
       <c r="G61" t="str">
         <v>Exact</v>
       </c>
     </row>
-    <row r="62" xml:space="preserve">
-      <c r="A62" t="str" xml:space="preserve">
+    <row r="62">
+      <c r="A62" t="str">
+        <v>06/18/2025</v>
+      </c>
+      <c r="B62" t="str">
+        <v>06/18/2025</v>
+      </c>
+      <c r="C62" t="str">
+        <v>$1,874.72</v>
+      </c>
+      <c r="D62" t="str">
+        <v>$1,874.72</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Deposit 06/18/2025</v>
+      </c>
+      <c r="F62" t="str">
+        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
+      </c>
+      <c r="G62" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="63" xml:space="preserve">
+      <c r="A63" t="str" xml:space="preserve">
         <v xml:space="preserve">06/18/2025
 -
 06/20/2025</v>
       </c>
-      <c r="B62" t="str">
+      <c r="B63" t="str">
         <v>06/20/2025</v>
       </c>
-      <c r="C62" t="str">
+      <c r="C63" t="str">
         <v>$14,195.21</v>
       </c>
-      <c r="D62" t="str">
+      <c r="D63" t="str">
         <v>$14,195.21</v>
       </c>
-      <c r="E62" t="str" xml:space="preserve">
+      <c r="E63" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $12,540.00 (Wellmed CC 06/18/2025 | 6/18)
 2: $1,655.21 (Credit Card 06/20/2025 With B#13351- Actual $ 14195.21 | 6/20)</v>
       </c>
-      <c r="F62" t="str">
+      <c r="F63" t="str">
         <v>BANKCARDBTOT DEP</v>
       </c>
-      <c r="G62" t="str">
+      <c r="G63" t="str">
         <v>Many-to-One</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>06/18/2025</v>
-      </c>
-      <c r="B63" t="str">
-        <v>06/18/2025</v>
-      </c>
-      <c r="C63" t="str">
-        <v>$1,874.72</v>
-      </c>
-      <c r="D63" t="str">
-        <v>$1,874.72</v>
-      </c>
-      <c r="E63" t="str">
-        <v>Deposit 06/18/2025</v>
-      </c>
-      <c r="F63" t="str">
-        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
-      </c>
-      <c r="G63" t="str">
-        <v>Exact</v>
       </c>
     </row>
     <row r="64">
@@ -3160,19 +3160,19 @@
         <v>06/18/2025</v>
       </c>
       <c r="B64" t="str">
-        <v>06/18/2025</v>
+        <v>06/20/2025</v>
       </c>
       <c r="C64" t="str">
-        <v>$818.00</v>
+        <v>$21,089.63</v>
       </c>
       <c r="D64" t="str">
-        <v>$818.00</v>
+        <v>$21,089.63</v>
       </c>
       <c r="E64" t="str">
-        <v>RFMS 06/18/2025</v>
+        <v>STATE OF FLORIDA MEDICAID 06/18/2025</v>
       </c>
       <c r="F64" t="str">
-        <v>NATL DATACARE CRT#A DEP RECORD #D</v>
+        <v>ACH MEDICAIDHCCLAIMPMT TRN***~LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G64" t="str">
         <v>Exact</v>
@@ -3232,16 +3232,16 @@
         <v>06/20/2025</v>
       </c>
       <c r="C67" t="str">
-        <v>$268,419.37</v>
+        <v>$227.25</v>
       </c>
       <c r="D67" t="str">
-        <v>$268,419.37</v>
+        <v>$227.25</v>
       </c>
       <c r="E67" t="str">
-        <v>FL Community Care 05/27/2025</v>
+        <v>NDC SPLIT DEP 06/20/2025</v>
       </c>
       <c r="F67" t="str">
-        <v>-</v>
+        <v>NDC SPLIT DEP INV#I</v>
       </c>
       <c r="G67" t="str">
         <v>Exact</v>
@@ -3252,19 +3252,19 @@
         <v>06/20/2025</v>
       </c>
       <c r="B68" t="str">
-        <v>06/20/2025</v>
+        <v>06/23/2025</v>
       </c>
       <c r="C68" t="str">
-        <v>$227.25</v>
+        <v>$14,256.93</v>
       </c>
       <c r="D68" t="str">
-        <v>$227.25</v>
+        <v>$14,256.93</v>
       </c>
       <c r="E68" t="str">
-        <v>NDC SPLIT DEP 06/20/2025</v>
+        <v>WPS GHA - MAC J5 PART A 06/20/2025</v>
       </c>
       <c r="F68" t="str">
-        <v>NDC SPLIT DEP INV#I</v>
+        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G68" t="str">
         <v>Exact</v>
@@ -3275,19 +3275,19 @@
         <v>06/20/2025</v>
       </c>
       <c r="B69" t="str">
-        <v>06/23/2025</v>
+        <v>06/20/2025</v>
       </c>
       <c r="C69" t="str">
-        <v>$14,256.93</v>
+        <v>$268,419.37</v>
       </c>
       <c r="D69" t="str">
-        <v>$14,256.93</v>
+        <v>$268,419.37</v>
       </c>
       <c r="E69" t="str">
-        <v>WPS GHA - MAC J5 PART A 06/20/2025</v>
+        <v>FL Community Care 05/27/2025</v>
       </c>
       <c r="F69" t="str">
-        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~LADY LAKE SPECIALTY CA</v>
+        <v>-</v>
       </c>
       <c r="G69" t="str">
         <v>Exact</v>
@@ -3301,16 +3301,16 @@
         <v>06/23/2025</v>
       </c>
       <c r="C70" t="str">
-        <v>$32,368.95</v>
+        <v>$3,386.00</v>
       </c>
       <c r="D70" t="str">
-        <v>$32,368.95</v>
+        <v>$3,386.00</v>
       </c>
       <c r="E70" t="str">
-        <v>Deposit 06/23/2025</v>
+        <v>UNITEDHEALTHCARE 06/23/2025</v>
       </c>
       <c r="F70" t="str">
-        <v>LADY LAKE SPECIASETTLEMENT</v>
+        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G70" t="str">
         <v>Exact</v>
@@ -3347,16 +3347,16 @@
         <v>06/23/2025</v>
       </c>
       <c r="C72" t="str">
-        <v>$3,386.00</v>
+        <v>$32,368.95</v>
       </c>
       <c r="D72" t="str">
-        <v>$3,386.00</v>
+        <v>$32,368.95</v>
       </c>
       <c r="E72" t="str">
-        <v>UNITEDHEALTHCARE 06/23/2025</v>
+        <v>Deposit 06/23/2025</v>
       </c>
       <c r="F72" t="str">
-        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
+        <v>LADY LAKE SPECIASETTLEMENT</v>
       </c>
       <c r="G72" t="str">
         <v>Exact</v>
@@ -3393,16 +3393,16 @@
         <v>06/24/2025</v>
       </c>
       <c r="C74" t="str">
-        <v>$13,905.65</v>
+        <v>$400.00</v>
       </c>
       <c r="D74" t="str">
-        <v>$13,905.65</v>
+        <v>$400.00</v>
       </c>
       <c r="E74" t="str">
-        <v>UNITEDHEALTHCARE COMMUNITY PLAN 06/24/2025</v>
+        <v>UNITED HEALTHCARE INSURANCE COMPANY 06/24/ 2025</v>
       </c>
       <c r="F74" t="str">
-        <v>UHC COMMUNITY PLHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
+        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**T**\LADYLAKE SPECIALTY CA</v>
       </c>
       <c r="G74" t="str">
         <v>Exact</v>
@@ -3416,16 +3416,16 @@
         <v>06/24/2025</v>
       </c>
       <c r="C75" t="str">
-        <v>$400.00</v>
+        <v>$13,905.65</v>
       </c>
       <c r="D75" t="str">
-        <v>$400.00</v>
+        <v>$13,905.65</v>
       </c>
       <c r="E75" t="str">
-        <v>UNITED HEALTHCARE INSURANCE COMPANY 06/24/ 2025</v>
+        <v>UNITEDHEALTHCARE COMMUNITY PLAN 06/24/2025</v>
       </c>
       <c r="F75" t="str">
-        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**T**\LADYLAKE SPECIALTY CA</v>
+        <v>UHC COMMUNITY PLHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G75" t="str">
         <v>Exact</v>
@@ -3459,19 +3459,19 @@
         <v>06/25/2025</v>
       </c>
       <c r="B77" t="str">
-        <v>06/26/2025</v>
+        <v>06/25/2025</v>
       </c>
       <c r="C77" t="str">
-        <v>$679.44</v>
+        <v>$628.50</v>
       </c>
       <c r="D77" t="str">
-        <v>$679.44</v>
+        <v>$628.50</v>
       </c>
       <c r="E77" t="str">
-        <v>STATE OF FLORIDA MEDICAID 06/25/2025</v>
+        <v>UNITEDHEALTHCARE COMMUNITY PLAN 06/25/2025</v>
       </c>
       <c r="F77" t="str">
-        <v>ACH MEDICAIDHCCLAIMPMT TRN***~LADY LAKE SPECIALTY CA</v>
+        <v>UHC COMMUNITY PLHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G77" t="str">
         <v>Exact</v>
@@ -3482,19 +3482,19 @@
         <v>06/25/2025</v>
       </c>
       <c r="B78" t="str">
-        <v>06/30/2025</v>
+        <v>06/26/2025</v>
       </c>
       <c r="C78" t="str">
-        <v>$976.36</v>
+        <v>$679.44</v>
       </c>
       <c r="D78" t="str">
-        <v>$976.36</v>
+        <v>$679.44</v>
       </c>
       <c r="E78" t="str">
-        <v>HUMANA INC. 06/25/2025</v>
+        <v>STATE OF FLORIDA MEDICAID 06/25/2025</v>
       </c>
       <c r="F78" t="str">
-        <v>HMPHCCLAIMPMT TRN***\LADY LAKE SPECIALTY CA</v>
+        <v>ACH MEDICAIDHCCLAIMPMT TRN***~LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G78" t="str">
         <v>Exact</v>
@@ -3505,19 +3505,19 @@
         <v>06/25/2025</v>
       </c>
       <c r="B79" t="str">
-        <v>06/25/2025</v>
+        <v>06/30/2025</v>
       </c>
       <c r="C79" t="str">
-        <v>$5,535.01</v>
+        <v>$976.36</v>
       </c>
       <c r="D79" t="str">
-        <v>$5,535.01</v>
+        <v>$976.36</v>
       </c>
       <c r="E79" t="str">
-        <v>Deposit 06/25/2025</v>
+        <v>HUMANA INC. 06/25/2025</v>
       </c>
       <c r="F79" t="str">
-        <v>LADY LAKE SPECIASETTLEMENT</v>
+        <v>HMPHCCLAIMPMT TRN***\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G79" t="str">
         <v>Exact</v>
@@ -3531,16 +3531,16 @@
         <v>06/25/2025</v>
       </c>
       <c r="C80" t="str">
-        <v>$628.50</v>
+        <v>$5,535.01</v>
       </c>
       <c r="D80" t="str">
-        <v>$628.50</v>
+        <v>$5,535.01</v>
       </c>
       <c r="E80" t="str">
-        <v>UNITEDHEALTHCARE COMMUNITY PLAN 06/25/2025</v>
+        <v>Deposit 06/25/2025</v>
       </c>
       <c r="F80" t="str">
-        <v>UHC COMMUNITY PLHCCLAIMPMT TRN**B**\LADY LAKE SPECIALTY CA</v>
+        <v>LADY LAKE SPECIASETTLEMENT</v>
       </c>
       <c r="G80" t="str">
         <v>Exact</v>
@@ -3554,16 +3554,16 @@
         <v>06/26/2025</v>
       </c>
       <c r="C81" t="str">
-        <v>$9,008.50</v>
+        <v>$120.00</v>
       </c>
       <c r="D81" t="str">
-        <v>$9,008.50</v>
+        <v>$120.00</v>
       </c>
       <c r="E81" t="str">
-        <v>AARP SUPPLEMENTAL HEALTH PLANS FROM UNITEDHEALTHCARE 06/26/2025</v>
+        <v>Deposit 06/26/2025</v>
       </c>
       <c r="F81" t="str">
-        <v>AARP SUPPLEMENTAHCCLAIMPMT TRN****\LADY LAKE SPECIALTY CA</v>
+        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
       </c>
       <c r="G81" t="str">
         <v>Exact</v>
@@ -3577,16 +3577,16 @@
         <v>06/26/2025</v>
       </c>
       <c r="C82" t="str">
-        <v>$120.00</v>
+        <v>$9,008.50</v>
       </c>
       <c r="D82" t="str">
-        <v>$120.00</v>
+        <v>$9,008.50</v>
       </c>
       <c r="E82" t="str">
-        <v>Deposit 06/26/2025</v>
+        <v>AARP SUPPLEMENTAL HEALTH PLANS FROM UNITEDHEALTHCARE 06/26/2025</v>
       </c>
       <c r="F82" t="str">
-        <v>LADY LAKE SPECIASETTLEMENT LADY LAKE SPECIALTY CA RECIPIENT</v>
+        <v>AARP SUPPLEMENTAHCCLAIMPMT TRN****\LADY LAKE SPECIALTY CA</v>
       </c>
       <c r="G82" t="str">
         <v>Exact</v>
@@ -3737,7 +3737,7 @@
         <v>06/26/2025</v>
       </c>
       <c r="B2" t="str">
-        <v>$900.00</v>
+        <v>$156.97</v>
       </c>
       <c r="C2" t="str">
         <v>RFMS 06/25/2025</v>
@@ -3751,7 +3751,7 @@
         <v>06/26/2025</v>
       </c>
       <c r="B3" t="str">
-        <v>$156.97</v>
+        <v>$900.00</v>
       </c>
       <c r="C3" t="str">
         <v>RFMS 06/25/2025</v>
@@ -3840,7 +3840,7 @@
         <v>06/02/2025</v>
       </c>
       <c r="B2" t="str">
-        <v>$-120.00</v>
+        <v>-$120.00</v>
       </c>
       <c r="C2" t="str">
         <v>NSF 06/02/2025</v>
@@ -3851,7 +3851,7 @@
         <v>06/06/2025</v>
       </c>
       <c r="B3" t="str">
-        <v>$-1,469.75</v>
+        <v>-$1,469.75</v>
       </c>
       <c r="C3" t="str">
         <v>nsf 06/06/2025</v>
@@ -3862,7 +3862,7 @@
         <v>06/25/2025</v>
       </c>
       <c r="B4" t="str">
-        <v>$-2,410.67</v>
+        <v>-$2,410.67</v>
       </c>
       <c r="C4" t="str">
         <v>nsf 06/25/2025</v>
@@ -3895,7 +3895,7 @@
         <v>06/16/2025</v>
       </c>
       <c r="B2" t="str">
-        <v>$-780.00</v>
+        <v>-$780.00</v>
       </c>
       <c r="C2" t="str">
         <v>Batch#13331 - Deposit 06/16/2025 * Reversals *</v>
@@ -3917,10 +3917,10 @@
         <v>06/18/2025</v>
       </c>
       <c r="B4" t="str">
-        <v>$831.21</v>
+        <v>-$7,577.20</v>
       </c>
       <c r="C4" t="str">
-        <v>Credit Card 06/18/2025</v>
+        <v>Batch#13373 - Credit Card 06/20/2025 * Reversals *</v>
       </c>
     </row>
     <row r="5">
@@ -3928,7 +3928,7 @@
         <v>06/18/2025</v>
       </c>
       <c r="B5" t="str">
-        <v>$-831.21</v>
+        <v>-$831.21</v>
       </c>
       <c r="C5" t="str">
         <v>Batch#13352 - Credit Card 06/18/2025 * Reversals *</v>
@@ -3939,10 +3939,10 @@
         <v>06/18/2025</v>
       </c>
       <c r="B6" t="str">
-        <v>$618.00</v>
+        <v>-$618.00</v>
       </c>
       <c r="C6" t="str">
-        <v>Credit Card 06/18/2025</v>
+        <v>Batch#13353 - Credit Card 06/18/2025 * Reversals *</v>
       </c>
     </row>
     <row r="7">
@@ -3950,10 +3950,10 @@
         <v>06/18/2025</v>
       </c>
       <c r="B7" t="str">
-        <v>$-618.00</v>
+        <v>-$206.00</v>
       </c>
       <c r="C7" t="str">
-        <v>Batch#13353 - Credit Card 06/18/2025 * Reversals *</v>
+        <v>Batch#13354 - Credit Card 06/18/2025 * Reversals *</v>
       </c>
     </row>
     <row r="8">
@@ -3972,10 +3972,10 @@
         <v>06/18/2025</v>
       </c>
       <c r="B9" t="str">
-        <v>$-206.00</v>
+        <v>$618.00</v>
       </c>
       <c r="C9" t="str">
-        <v>Batch#13354 - Credit Card 06/18/2025 * Reversals *</v>
+        <v>Credit Card 06/18/2025</v>
       </c>
     </row>
     <row r="10">
@@ -3983,10 +3983,10 @@
         <v>06/18/2025</v>
       </c>
       <c r="B10" t="str">
-        <v>$-7,577.20</v>
+        <v>$831.21</v>
       </c>
       <c r="C10" t="str">
-        <v>Batch#13373 - Credit Card 06/20/2025 * Reversals *</v>
+        <v>Credit Card 06/18/2025</v>
       </c>
     </row>
     <row r="11">
@@ -3994,10 +3994,10 @@
         <v>06/20/2025</v>
       </c>
       <c r="B11" t="str">
-        <v>$2,410.67</v>
+        <v>-$2,410.67</v>
       </c>
       <c r="C11" t="str">
-        <v>Credit Card 06/20/2025</v>
+        <v>Batch#13368 - Credit Card 06/20/2025 * Reversals *</v>
       </c>
     </row>
     <row r="12">
@@ -4005,10 +4005,10 @@
         <v>06/20/2025</v>
       </c>
       <c r="B12" t="str">
-        <v>$-2,410.67</v>
+        <v>$2,410.67</v>
       </c>
       <c r="C12" t="str">
-        <v>Batch#13368 - Credit Card 06/20/2025 * Reversals *</v>
+        <v>Credit Card 06/20/2025</v>
       </c>
     </row>
     <row r="13">
